--- a/test/fixture/snapshot/cli/sort-format/collection-high-value/commander/commander-common.xlsx
+++ b/test/fixture/snapshot/cli/sort-format/collection-high-value/commander/commander-common.xlsx
@@ -60,15 +60,15 @@
           <t xml:space="preserve">Border: black
 Finish: normal
 Keywords:
-➤ Scry</t>
+➤ Devoid</t>
         </r>
       </text>
     </comment>
     <comment ref="E3" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">When this artifact enters, scry 2. (Look at the top two cards of your library, then put any number of them on the bottom and the rest on top in any order.)
-Whenever another artifact you control enters, this artifact becomes a 4/4 Phyrexian Eye artifact creature until end of turn.</t>
+          <t xml:space="preserve">Devoid (This card has no color.)
+Counter target spell unless its controller pays {1}. You create a 1/1 colorless Eldrazi Scion creature token. It has "Sacrifice this token: Add {C}." ({C} represents colorless mana.)</t>
         </r>
       </text>
     </comment>
@@ -83,6 +83,32 @@
     <comment ref="D4" authorId="0">
       <text>
         <r>
+          <t xml:space="preserve">Border: black
+Finish: normal
+Keywords:
+➤ Scry</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">When this artifact enters, scry 2. (Look at the top two cards of your library, then put any number of them on the bottom and the rest on top in any order.)
+Whenever another artifact you control enters, this artifact becomes a 4/4 Phyrexian Eye artifact creature until end of turn.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I4" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">➤ 2 generic
+➤ 1 blue</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0">
+      <text>
+        <r>
           <t xml:space="preserve">P/T: 1/1
 Border: black
 Finish: normal
@@ -92,7 +118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E4" authorId="0">
+    <comment ref="E5" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Flying
@@ -100,7 +126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I4" authorId="0">
+    <comment ref="I5" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 2 generic
@@ -330,7 +356,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="118">
   <si>
     <t>Commander (Common) - White</t>
   </si>
@@ -410,6 +436,33 @@
     <t>Commander (Common) - Blue</t>
   </si>
   <si>
+    <t>Abstruse Interference</t>
+  </si>
+  <si>
+    <t>ogw</t>
+  </si>
+  <si>
+    <t>Oath of the Gatewatch</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>{2}{U}</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>Open Abstruse Interference</t>
+  </si>
+  <si>
     <t>Eye of Malcator</t>
   </si>
   <si>
@@ -423,12 +476,6 @@
   </si>
   <si>
     <t>50</t>
-  </si>
-  <si>
-    <t>{2}{U}</t>
-  </si>
-  <si>
-    <t>U</t>
   </si>
   <si>
     <t>0.03</t>
@@ -549,9 +596,6 @@
   </si>
   <si>
     <t>255</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>U, W</t>
@@ -773,7 +817,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -796,12 +840,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4493,10 +4531,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N204"/>
+  <dimension ref="A1:N205"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -4508,7 +4546,7 @@
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="20" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="14" max="14" width="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -4584,28 +4622,28 @@
         <v>16</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>31</v>
       </c>
       <c r="J3" s="9">
         <v>3</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L3" s="9" t="s">
         <v>32</v>
@@ -4631,19 +4669,19 @@
         <v>36</v>
       </c>
       <c r="E4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="G4" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="11" t="s">
-        <v>40</v>
-      </c>
       <c r="I4" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J4" s="11">
         <v>3</v>
@@ -4655,27 +4693,55 @@
         <v>32</v>
       </c>
       <c r="M4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="N4" s="11" t="s">
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+      <c r="B5" s="7">
+        <v>1</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="7">
+        <v>3</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -7861,6 +7927,22 @@
       <c r="M204" s="1"/>
       <c r="N204" s="1"/>
     </row>
+    <row r="205" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="1"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1"/>
+      <c r="E205" s="1"/>
+      <c r="F205" s="1"/>
+      <c r="G205" s="1"/>
+      <c r="H205" s="1"/>
+      <c r="I205" s="1"/>
+      <c r="J205" s="1"/>
+      <c r="K205" s="1"/>
+      <c r="L205" s="1"/>
+      <c r="M205" s="1"/>
+      <c r="N205" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
@@ -7868,10 +7950,11 @@
   <hyperlinks>
     <hyperlink ref="N3" r:id="rId1"/>
     <hyperlink ref="N4" r:id="rId2"/>
+    <hyperlink ref="N5" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -7896,7 +7979,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7958,7 +8041,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="9">
         <v>1</v>
@@ -7967,86 +8050,86 @@
         <v>16</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J3" s="9">
         <v>5</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="13" t="s">
+      <c r="D4" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="11">
+        <v>2</v>
+      </c>
+      <c r="K4" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="J4" s="13">
-        <v>2</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>59</v>
+      <c r="L4" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B5" s="7">
         <v>1</v>
@@ -8061,31 +8144,31 @@
         <v>17</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="J5" s="7">
         <v>1</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -11324,7 +11407,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11386,7 +11469,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B3" s="9">
         <v>1</v>
@@ -11395,86 +11478,86 @@
         <v>16</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="J3" s="9">
         <v>0</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M3" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="B4" s="13">
+        <v>1</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="15">
-        <v>1</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="E4" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="J4" s="15">
+      <c r="G4" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="13">
         <v>0</v>
       </c>
-      <c r="K4" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="N4" s="15" t="s">
-        <v>76</v>
+      <c r="K4" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B5" s="9">
         <v>1</v>
@@ -11483,86 +11566,86 @@
         <v>16</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="J5" s="9">
         <v>0</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="13">
+      <c r="A6" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="11">
         <v>1</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J6" s="13">
+      <c r="D6" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="11">
         <v>0</v>
       </c>
-      <c r="K6" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="N6" s="13" t="s">
-        <v>92</v>
+      <c r="K6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B7" s="9">
         <v>1</v>
@@ -11571,86 +11654,86 @@
         <v>16</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="J7" s="9">
         <v>0</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="13">
+      <c r="A8" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="11">
         <v>1</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J8" s="13">
+      <c r="D8" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="11">
         <v>0</v>
       </c>
-      <c r="K8" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>105</v>
+      <c r="K8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B9" s="7">
         <v>1</v>
@@ -11659,37 +11742,37 @@
         <v>16</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="J9" s="7">
         <v>0</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
